--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -43030,12 +43030,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -52761,12 +52761,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -52835,12 +52835,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -79801,12 +79801,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -49102,12 +49102,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -52868,12 +52868,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -55203,12 +55203,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -86998,12 +86998,12 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_0501_1000" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1001_1500" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1501_2000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2386" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2388" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42697,12 +42697,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -55203,12 +55203,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -73792,7 +73792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K387"/>
+  <dimension ref="A1:K389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -79055,22 +79055,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>海昌生技</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -79083,31 +79083,27 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>海昌生技</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -79120,32 +79116,36 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>精誠金融</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -79153,36 +79153,32 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>精誠金融</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -79190,27 +79186,31 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -79223,36 +79223,32 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -79269,22 +79265,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -79306,22 +79302,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -79343,27 +79339,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -79380,27 +79376,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -79417,22 +79413,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>永悅健康-創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -79454,12 +79450,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>永悅健康-創</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -79491,27 +79487,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -79519,27 +79515,31 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -79557,27 +79557,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -79585,21 +79585,17 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -79631,22 +79627,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -79668,12 +79664,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -79705,22 +79701,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -79742,12 +79738,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -79765,44 +79761,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>半導體設備_CoWoS</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>晶圓再生</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -79824,63 +79812,67 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>都有</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr"/>
+          <t>半導體設備_CoWoS</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>晶圓再生</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -79902,59 +79894,63 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
+          <t>都有</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -79962,40 +79958,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -80017,12 +80009,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -80042,38 +80034,38 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>被動元件</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>電容</t>
-        </is>
-      </c>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -80081,40 +80073,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>被動元件</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -80122,36 +80110,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>被動元件</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>電容</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -80159,36 +80151,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>被動元件</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -80196,40 +80192,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -80251,22 +80243,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -80274,36 +80266,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -80325,22 +80321,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -80362,22 +80358,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -80399,22 +80395,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -80436,22 +80432,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -80473,27 +80469,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -80501,27 +80497,31 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -80543,27 +80543,27 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -80571,31 +80571,27 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -80617,12 +80613,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -80654,22 +80650,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -80691,12 +80687,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -80728,12 +80724,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -80765,22 +80761,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -80802,27 +80798,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -80839,27 +80835,27 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>泰霖</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -80876,27 +80872,27 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -80913,27 +80909,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>瑞穎</t>
+          <t>泰霖</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -80950,22 +80946,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -80987,22 +80983,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>瑞穎</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -81024,22 +81020,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -81047,45 +81043,41 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>低軌衛星</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -81093,17 +81085,21 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -81121,41 +81117,45 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>低軌衛星</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -81163,21 +81163,17 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -81209,22 +81205,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -81246,22 +81242,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -81283,22 +81279,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -81320,22 +81316,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -81357,22 +81353,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>大世科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -81394,12 +81390,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -81431,22 +81427,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>大世科</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -81468,22 +81464,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -81505,22 +81501,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -81542,22 +81538,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -81579,22 +81575,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>大億金茂</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -81616,22 +81612,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -81653,22 +81649,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>大億金茂</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -81690,22 +81686,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -81727,22 +81723,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -81764,22 +81760,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -81801,22 +81797,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -81838,22 +81834,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -81875,12 +81871,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -81912,12 +81908,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -81935,30 +81931,26 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -81990,12 +81982,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -82013,36 +82005,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -82064,27 +82060,27 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -82092,27 +82088,31 @@
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -82134,27 +82134,27 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -82162,31 +82162,27 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -82208,22 +82204,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -82245,22 +82241,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -82282,22 +82278,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -82319,22 +82315,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -82356,22 +82352,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -82379,40 +82375,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -82434,22 +82426,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -82457,36 +82449,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -82508,22 +82504,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -82545,22 +82541,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -82582,22 +82578,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -82605,16 +82601,8 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>功率元件/二極體</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>MOSFET</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
@@ -82627,22 +82615,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>朋程</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -82650,40 +82638,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>全景軟體</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -82691,8 +82675,16 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>功率元件/二極體</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
@@ -82705,12 +82697,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -82728,41 +82720,45 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>生展</t>
+          <t>全景軟體</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -82779,22 +82775,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -82816,27 +82812,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>生展</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -82853,22 +82849,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>三竹</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -82890,22 +82886,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -82913,45 +82909,41 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -82959,60 +82951,72 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>恒耀國際</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -83025,21 +83029,17 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -83067,63 +83067,59 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>恒耀國際</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>冠好</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -83136,31 +83132,27 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -83168,41 +83160,45 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -83219,27 +83215,27 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -83247,32 +83243,36 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -83280,27 +83280,31 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>盛弘</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -83313,21 +83317,17 @@
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -83355,12 +83355,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>盛弘</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -83392,27 +83392,27 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -83420,31 +83420,27 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -83457,32 +83453,36 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -83499,27 +83499,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>實威</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -83527,31 +83527,27 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>旭源</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -83564,32 +83560,36 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>實威</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -83597,27 +83597,31 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>旭源</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -83635,22 +83639,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -83663,31 +83667,27 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>紅木-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -83705,22 +83705,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -83742,27 +83742,27 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -83770,31 +83770,27 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -83816,27 +83812,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>弘帆</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -83844,27 +83840,31 @@
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>鉅邁</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -83877,27 +83877,31 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>大江</t>
+          <t>弘帆</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -83910,21 +83914,17 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>大地-KY</t>
+          <t>鉅邁</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -83952,22 +83952,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>大江</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -83980,27 +83980,31 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>大地-KY</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -84018,22 +84022,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -84051,22 +84055,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -84079,21 +84083,17 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -84121,22 +84121,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>華研</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -84149,27 +84149,31 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -84187,27 +84191,27 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>華研</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -84215,36 +84219,32 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -84252,36 +84252,32 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -84289,32 +84285,36 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -84322,27 +84322,31 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -84360,12 +84364,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -84393,22 +84397,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -84426,27 +84430,27 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>納維康</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -84454,31 +84458,27 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -84496,27 +84496,27 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>納維康</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -84524,32 +84524,36 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -84557,31 +84561,27 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -84599,27 +84599,27 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -84627,27 +84627,31 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -84665,27 +84669,27 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -84693,31 +84697,27 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -84735,27 +84735,27 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>三貝德</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -84763,32 +84763,36 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -84796,21 +84800,17 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>裕國</t>
+          <t>三貝德</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -84838,27 +84838,27 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>花王</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -84866,27 +84866,31 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>裕國</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -84899,21 +84903,17 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>光隆</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -84941,12 +84941,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -84978,12 +84978,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -85011,22 +85011,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -85039,27 +85039,31 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>大田</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -85077,22 +85081,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -85105,31 +85109,27 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>北基</t>
+          <t>大田</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -85142,31 +85142,27 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>鉅明</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -85179,27 +85175,31 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>北基</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -85212,27 +85212,31 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>青鋼</t>
+          <t>鉅明</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -85245,31 +85249,27 @@
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>富堡</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -85282,36 +85282,32 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>青鋼</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -85328,22 +85324,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -85356,32 +85352,36 @@
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>邦泰</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -85389,27 +85389,31 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -85427,12 +85431,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>合騏*</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -85460,22 +85464,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>明安</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -85493,22 +85497,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>合騏*</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -85521,31 +85525,27 @@
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>關中</t>
+          <t>明安</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -85563,22 +85563,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>森鉅</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -85591,68 +85591,64 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>關中</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>散熱液冷</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>森鉅</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -85665,68 +85661,68 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>910322</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>康師傅-DR</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>散熱液冷</t>
+        </is>
+      </c>
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -85739,17 +85735,21 @@
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>910322</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>康師傅-DR</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -85781,22 +85781,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>存託憑證</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -85809,21 +85809,17 @@
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>910861</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
+          <t>神州-DR</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -85855,12 +85851,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>泰聚亨-DR</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -85892,12 +85888,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>911868</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>同方友友-DR</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -85929,12 +85925,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>912000</t>
+          <t>911622</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>晨訊科-DR</t>
+          <t>泰聚亨-DR</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -85966,12 +85962,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>911868</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>同方友友-DR</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -86003,22 +85999,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>912000</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>晨訊科-DR</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -86031,27 +86027,31 @@
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86064,17 +86064,21 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -86102,12 +86106,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -86135,22 +86139,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -86163,31 +86167,27 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -86205,22 +86205,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -86242,22 +86242,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -86275,22 +86275,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -86303,32 +86303,36 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -86336,31 +86340,27 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -86378,27 +86378,27 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -86406,27 +86406,31 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -86439,31 +86443,27 @@
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86481,22 +86481,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>巨大</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86509,27 +86509,31 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>福興</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -86547,22 +86551,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -86580,22 +86584,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>福興</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86608,21 +86612,17 @@
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>泰銘</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -86650,22 +86650,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>中視</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86678,17 +86678,21 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>泰銘</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -86716,22 +86720,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>中視</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -86749,22 +86753,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -86777,31 +86781,27 @@
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -86819,22 +86819,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>成霖</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -86847,27 +86847,31 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>慶豐富</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -86885,22 +86889,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>全國</t>
+          <t>成霖</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -86913,31 +86917,27 @@
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>百和</t>
+          <t>慶豐富</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -86955,22 +86955,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -86983,17 +86983,21 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>百和</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -87021,22 +87025,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -87054,12 +87058,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -87087,22 +87091,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>好樂迪</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -87115,21 +87119,17 @@
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>新麗</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -87157,22 +87157,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>好樂迪</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -87185,27 +87185,31 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>三發地產</t>
+          <t>新麗</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -87218,31 +87222,27 @@
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -87260,22 +87260,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>萬國通</t>
+          <t>三發地產</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -87297,27 +87297,27 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -87325,31 +87325,27 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>萬國通</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -87362,32 +87358,36 @@
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>世紀鋼</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -87404,22 +87404,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>邁達康</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -87437,12 +87437,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>有益</t>
+          <t>世紀鋼</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -87471,6 +87471,76 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>9960</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>邁達康</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>有益</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -43063,12 +43063,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -79065,17 +79065,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -79083,7 +79083,11 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -79904,12 +79908,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -52794,12 +52794,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -52868,12 +52868,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -24000,12 +24000,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -43063,12 +43063,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -52794,12 +52794,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -11371,12 +11371,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -43063,12 +43063,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -52868,12 +52868,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -85478,12 +85478,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -11371,12 +11371,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -24000,12 +24000,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -52868,12 +52868,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -55869,12 +55869,12 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -68379,12 +68379,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -85478,12 +85478,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -86767,12 +86767,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_0501_1000" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1001_1500" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1501_2000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2388" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2387" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42697,12 +42697,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -43063,12 +43063,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -49102,12 +49102,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -52218,12 +52218,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -52646,12 +52646,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52683,12 +52683,12 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>金融業</t>
+          <t>金融保險業</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -55203,12 +55203,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -68379,12 +68379,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -73792,7 +73792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K389"/>
+  <dimension ref="A1:K388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -79908,12 +79908,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -82245,12 +82245,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -82282,22 +82282,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -82319,22 +82319,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -82356,22 +82356,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -82393,22 +82393,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -82416,36 +82416,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -82453,40 +82457,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -82508,22 +82508,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -82545,22 +82545,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -82582,22 +82582,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>朋程</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -82619,22 +82619,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -82642,8 +82642,16 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>功率元件/二極體</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
@@ -82656,12 +82664,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -82681,42 +82689,38 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>功率元件/二極體</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>MOSFET</t>
-        </is>
-      </c>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>全景軟體</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -82724,40 +82728,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>全景軟體</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -82779,27 +82779,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>生展</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -82816,27 +82816,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>生展</t>
+          <t>三竹</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -82853,22 +82853,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -82890,12 +82890,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -82927,22 +82927,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -82950,77 +82950,73 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -83038,22 +83034,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>恒耀國際</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -83066,27 +83062,31 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>恒耀國際</t>
+          <t>冠好</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -83099,110 +83099,110 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -83219,22 +83219,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -83256,27 +83256,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -83284,31 +83284,27 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -83326,22 +83322,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>盛弘</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -83354,27 +83350,31 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>盛弘</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -83387,31 +83387,27 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -83424,32 +83420,36 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -83466,27 +83466,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -83494,31 +83494,27 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -83531,32 +83527,36 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>實威</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -83573,27 +83573,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>實威</t>
+          <t>旭源</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -83601,31 +83601,27 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>旭源</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -83643,12 +83639,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -83676,22 +83672,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -83704,27 +83700,31 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -83737,31 +83737,27 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>紅木-KY</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -83774,32 +83770,36 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -83816,27 +83816,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -83853,22 +83853,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>弘帆</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -83881,31 +83881,27 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>弘帆</t>
+          <t>鉅邁</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -83923,22 +83919,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>鉅邁</t>
+          <t>大江</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -83951,27 +83947,31 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>大江</t>
+          <t>大地-KY</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -83984,31 +83984,27 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>大地-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -84026,12 +84022,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -84059,22 +84055,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -84092,22 +84088,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -84120,27 +84116,31 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -84153,31 +84153,27 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>華研</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -84195,12 +84191,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>華研</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -84228,27 +84224,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -84256,27 +84252,31 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -84298,27 +84298,27 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -84326,31 +84326,27 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -84368,22 +84364,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -84401,22 +84397,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -84434,22 +84430,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -84467,27 +84463,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>納維康</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -84495,32 +84491,36 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>納維康</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -84528,21 +84528,17 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -84570,27 +84566,27 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -84598,32 +84594,36 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -84631,31 +84631,27 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -84673,22 +84669,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -84706,27 +84702,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -84734,32 +84730,36 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -84767,21 +84767,17 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>三貝德</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -84809,27 +84805,27 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>三貝德</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -84837,32 +84833,36 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>裕國</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -84870,21 +84870,17 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>裕國</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -84912,22 +84908,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>花王</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -84940,27 +84936,31 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -84973,31 +84973,27 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>光隆</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -85010,27 +85006,31 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -85043,31 +85043,27 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -85085,22 +85081,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>大田</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -85118,22 +85114,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>大田</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -85146,17 +85142,21 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>北基</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -85188,22 +85188,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>北基</t>
+          <t>鉅明</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -85216,31 +85216,27 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>鉅明</t>
+          <t>富堡</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -85258,22 +85254,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>青鋼</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -85286,27 +85282,31 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>青鋼</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -85328,27 +85328,27 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -85365,27 +85365,27 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -85393,31 +85393,27 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -85435,12 +85431,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>邦泰</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -85468,12 +85464,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>合騏*</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -85501,22 +85497,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>合騏*</t>
+          <t>明安</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -85534,22 +85530,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>明安</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -85562,27 +85558,31 @@
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>關中</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -85595,31 +85595,27 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>關中</t>
+          <t>森鉅</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85637,86 +85633,90 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>森鉅</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>散熱液冷</t>
+        </is>
+      </c>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>散熱液冷</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>910322</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>康師傅-DR</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -85748,12 +85748,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>910322</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>康師傅-DR</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -85785,22 +85785,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>910861</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>神州-DR</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>存託憑證</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -85813,17 +85813,21 @@
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -85855,12 +85859,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -85892,12 +85896,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>911622</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
+          <t>泰聚亨-DR</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -85929,12 +85933,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>911868</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>泰聚亨-DR</t>
+          <t>同方友友-DR</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -85966,12 +85970,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>911868</t>
+          <t>912000</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>同方友友-DR</t>
+          <t>晨訊科-DR</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -86003,12 +86007,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>912000</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>晨訊科-DR</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -86040,22 +86044,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86068,31 +86072,27 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86110,22 +86110,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86143,22 +86143,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -86176,22 +86176,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -86204,27 +86204,31 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -86237,31 +86241,27 @@
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -86274,27 +86274,31 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -86307,31 +86311,27 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -86349,27 +86349,27 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -86377,32 +86377,36 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -86410,31 +86414,27 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -86452,22 +86452,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86480,27 +86480,31 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86513,31 +86517,27 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -86555,22 +86555,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>巨大</t>
+          <t>福興</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -86588,22 +86588,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>福興</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86621,22 +86621,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -86649,27 +86649,31 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>泰銘</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86682,21 +86686,17 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>泰銘</t>
+          <t>中視</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -86724,12 +86724,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>中視</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -86757,22 +86757,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -86790,22 +86790,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -86818,27 +86818,31 @@
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -86851,31 +86855,27 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>成霖</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -86893,12 +86893,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>成霖</t>
+          <t>慶豐富</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -86926,22 +86926,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>慶豐富</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -86954,27 +86954,31 @@
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>全國</t>
+          <t>百和</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -86987,21 +86991,17 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>百和</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -87029,12 +87029,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -87062,22 +87062,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -87095,22 +87095,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -87128,22 +87128,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>好樂迪</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -87156,27 +87156,31 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>好樂迪</t>
+          <t>新麗</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -87189,31 +87193,27 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>新麗</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -87231,22 +87231,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>三發地產</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -87259,27 +87259,31 @@
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>三發地產</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -87292,31 +87296,27 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>萬國通</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -87329,32 +87329,36 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>萬國通</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -87371,27 +87375,27 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -87399,31 +87403,27 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>世紀鋼</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -87436,27 +87436,31 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>世紀鋼</t>
+          <t>邁達康</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -87469,31 +87473,27 @@
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>邁達康</t>
+          <t>有益</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -87506,40 +87506,7 @@
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>9962</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>有益</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr">
+      <c r="K388" t="inlineStr">
         <is>
           <t>provisional_industry_mapping</t>
         </is>

--- a/docs/latest/stock_theme_manual_fill_template_latest.xlsx
+++ b/docs/latest/stock_theme_manual_fill_template_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_0501_1000" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1001_1500" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_1501_2000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2387" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stocks_2001_2388" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16603,12 +16603,12 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -49102,12 +49102,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -52218,12 +52218,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -52646,12 +52646,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52683,12 +52683,12 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>金融保險業</t>
+          <t>金融業</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -55203,12 +55203,12 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -55869,12 +55869,12 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -73792,7 +73792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K388"/>
+  <dimension ref="A1:K389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -78985,27 +78985,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>精華生醫</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -79013,36 +79013,32 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>民盛</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -79050,32 +79046,36 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>稜研科技*-創</t>
+          <t>民盛</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -79083,36 +79083,32 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>海昌生技</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -79129,22 +79125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>海昌生技</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -79157,32 +79153,36 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>精誠金融</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -79190,36 +79190,32 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>精誠金融</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -79227,27 +79223,31 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>汽車工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -79260,36 +79260,32 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>汽車工業</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -79306,22 +79302,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -79343,22 +79339,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -79380,27 +79376,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -79417,27 +79413,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -79454,22 +79450,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>永悅健康-創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -79491,12 +79487,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>永悅健康-創</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -79528,27 +79524,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -79556,27 +79552,31 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>權證/衍生商品</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -79594,27 +79594,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>權證/衍生商品</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -79622,31 +79622,27 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -79668,22 +79664,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -79705,22 +79701,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -79742,22 +79738,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -79779,22 +79775,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -79816,22 +79812,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -79839,44 +79835,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>半導體設備_CoWoS</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>晶圓再生</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -79884,114 +79872,122 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>半導體設備_CoWoS</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>晶圓再生</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>都有</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>都有</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530;dual_industry_theme_identity</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -80013,12 +80009,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -80036,40 +80032,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -80077,36 +80069,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -80114,30 +80110,26 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>被動元件</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>電容</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -80160,35 +80152,35 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>電容</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -80196,36 +80188,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>被動元件</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -80247,22 +80243,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -80270,40 +80266,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -80311,36 +80303,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -80362,22 +80358,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -80399,22 +80395,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -80436,22 +80432,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -80473,22 +80469,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -80510,22 +80506,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -80547,27 +80543,27 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -80575,32 +80571,36 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -80608,21 +80608,17 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -80654,22 +80650,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -80691,22 +80687,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -80728,22 +80724,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -80765,22 +80761,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -80802,22 +80798,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -80839,22 +80835,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -80876,27 +80872,27 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -80913,22 +80909,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>泰霖</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -80950,27 +80946,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>泰霖</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -80987,22 +80983,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>瑞穎</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -81024,22 +81020,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>瑞穎</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -81061,22 +81057,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -81098,22 +81094,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -81121,78 +81117,82 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>低軌衛星</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>低軌衛星</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -81200,31 +81200,27 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -81246,22 +81242,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -81283,22 +81279,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -81320,22 +81316,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -81357,22 +81353,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -81394,22 +81390,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -81431,22 +81427,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>大世科</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -81468,22 +81464,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>大世科</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -81505,22 +81501,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -81542,22 +81538,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -81579,22 +81575,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -81616,12 +81612,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -81653,22 +81649,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>大億金茂</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -81690,22 +81686,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>大億金茂</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -81727,22 +81723,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -81764,22 +81760,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -81801,22 +81797,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>電子通路業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -81838,22 +81834,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>電子通路業</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -81875,22 +81871,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -81912,22 +81908,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -81949,22 +81945,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -81986,22 +81982,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -82009,40 +82005,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -82050,36 +82042,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -82101,22 +82097,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -82138,27 +82134,27 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -82166,32 +82162,36 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>通信網路業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -82199,31 +82199,27 @@
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>通信網路業</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -82245,22 +82241,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -82282,22 +82278,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -82319,22 +82315,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -82356,22 +82352,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -82393,22 +82389,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -82416,40 +82412,36 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>軍工無人機</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -82457,36 +82449,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>軍工無人機</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -82508,22 +82504,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -82545,22 +82541,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>光電業</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -82582,22 +82578,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -82619,22 +82615,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>朋程</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -82642,16 +82638,8 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>功率元件/二極體</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>MOSFET</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
@@ -82664,12 +82652,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -82689,38 +82677,42 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
+          <t>功率元件/二極體</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>全景軟體</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -82728,36 +82720,40 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>全景軟體</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -82779,27 +82775,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>生展</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -82816,27 +82812,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>生展</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -82853,22 +82849,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>三竹</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -82890,12 +82886,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -82927,22 +82923,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -82950,73 +82946,77 @@
           <t>主流</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>記憶體儲存</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>user_authorized_seed_20260530</t>
+          <t>provisional_industry_mapping</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>記憶體儲存</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>user_authorized_seed_20260530</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -83034,22 +83034,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>恒耀國際</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -83062,31 +83062,27 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>冠好</t>
+          <t>恒耀國際</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -83099,110 +83095,110 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>冠好</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>PCB_CCL_ABF材料</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>航運業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>PCB_CCL_ABF材料</t>
+        </is>
+      </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>航運業</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -83219,22 +83215,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>半導體業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -83256,27 +83252,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -83284,27 +83280,31 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -83322,22 +83322,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>盛弘</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -83350,31 +83350,27 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>盛弘</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -83387,27 +83383,31 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -83420,36 +83420,32 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -83466,27 +83462,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -83494,27 +83490,31 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -83527,36 +83527,32 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>實威</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -83573,27 +83569,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>旭源</t>
+          <t>實威</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>資訊服務業</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -83601,27 +83597,31 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>旭源</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -83639,12 +83639,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -83672,22 +83672,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -83700,31 +83700,27 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>紅木-KY</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -83737,27 +83733,31 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -83770,36 +83770,32 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -83816,27 +83812,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -83853,22 +83849,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>弘帆</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -83881,27 +83877,31 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>鉅邁</t>
+          <t>弘帆</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -83919,22 +83919,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>大江</t>
+          <t>鉅邁</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -83947,31 +83947,27 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>大地-KY</t>
+          <t>大江</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -83984,27 +83980,31 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>大地-KY</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -84022,12 +84022,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -84055,22 +84055,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -84088,22 +84088,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -84116,31 +84116,27 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -84153,27 +84149,31 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>華研</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -84191,12 +84191,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>華研</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -84224,27 +84224,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -84252,31 +84252,27 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -84298,27 +84294,27 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -84326,27 +84322,31 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -84364,22 +84364,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -84397,22 +84397,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -84430,22 +84430,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -84463,27 +84463,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>納維康</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -84491,36 +84491,32 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>納維康</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -84528,17 +84524,21 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -84566,27 +84566,27 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -84594,36 +84594,32 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -84631,27 +84627,31 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -84669,22 +84669,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -84702,27 +84702,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -84730,36 +84730,32 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -84767,17 +84763,21 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>三貝德</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -84805,27 +84805,27 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>三貝德</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -84833,36 +84833,32 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>裕國</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -84870,17 +84866,21 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>花王</t>
+          <t>裕國</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -84908,22 +84908,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -84936,31 +84936,27 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>光隆</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -84973,27 +84969,31 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -85006,31 +85006,27 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -85043,27 +85039,31 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -85081,22 +85081,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>大田</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -85114,22 +85114,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大田</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -85142,21 +85142,17 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>北基</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -85188,22 +85184,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>鉅明</t>
+          <t>北基</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -85216,27 +85212,31 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>鉅明</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -85254,22 +85254,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>青鋼</t>
+          <t>富堡</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -85282,31 +85282,27 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>青鋼</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -85328,27 +85324,27 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>數位雲端</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -85365,27 +85361,27 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>數位雲端</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -85393,27 +85389,31 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>邦泰</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -85431,12 +85431,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>邦泰</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -85464,12 +85464,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>合騏*</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -85497,22 +85497,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>明安</t>
+          <t>合騏*</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -85530,22 +85530,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>明安</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -85558,31 +85558,27 @@
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>關中</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -85595,27 +85591,31 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>森鉅</t>
+          <t>關中</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -85633,90 +85633,86 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>森鉅</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>主流</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>散熱液冷</t>
-        </is>
-      </c>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>user_authorized_seed_20260530</t>
-        </is>
-      </c>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DR / 外國上市</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>非主流</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr"/>
+          <t>主流</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>散熱液冷</t>
+        </is>
+      </c>
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>provisional_industry_mapping</t>
+          <t>user_authorized_seed_20260530</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>910322</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>康師傅-DR</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -85748,12 +85744,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>910322</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>康師傅-DR</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -85785,12 +85781,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -85822,12 +85818,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>910861</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>神州-DR</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -85859,12 +85855,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -85896,12 +85892,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>泰聚亨-DR</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -85933,12 +85929,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>911868</t>
+          <t>911622</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>同方友友-DR</t>
+          <t>泰聚亨-DR</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -85970,12 +85966,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>912000</t>
+          <t>911868</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>晨訊科-DR</t>
+          <t>同方友友-DR</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -86007,12 +86003,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>912000</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>晨訊科-DR</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -86044,22 +86040,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>DR / 外國上市</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -86072,27 +86068,31 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -86110,22 +86110,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -86143,22 +86143,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -86176,22 +86176,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -86204,31 +86204,27 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>包材 / 容器製造</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -86241,27 +86237,31 @@
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>包材 / 容器製造</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -86274,31 +86274,27 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -86311,27 +86307,31 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -86349,27 +86349,27 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -86377,36 +86377,32 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -86414,27 +86410,31 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>保全 / 智慧安防服務</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -86452,22 +86452,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>保全 / 智慧安防服務</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -86480,31 +86480,27 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -86517,27 +86513,31 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>巨大</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -86555,22 +86555,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>福興</t>
+          <t>巨大</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -86588,22 +86588,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>福興</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -86621,22 +86621,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -86649,31 +86649,27 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>泰銘</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -86686,17 +86682,21 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>中視</t>
+          <t>泰銘</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -86724,12 +86724,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>秋雨</t>
+          <t>中視</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -86757,22 +86757,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>秋雨</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -86790,22 +86790,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -86818,31 +86818,27 @@
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>欣高</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>工程承攬 / EPC服務</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -86855,27 +86851,31 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>成霖</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>工程承攬 / EPC服務</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -86893,12 +86893,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>慶豐富</t>
+          <t>成霖</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -86926,22 +86926,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>全國</t>
+          <t>慶豐富</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>油電燃氣業</t>
+          <t>居家生活</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -86954,31 +86954,27 @@
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>百和</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>油電燃氣業</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -86991,17 +86987,21 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>百和</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -87029,12 +87029,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -87062,22 +87062,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>汽車金融 / 分期租賃</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -87095,22 +87095,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>汽車金融 / 分期租賃</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -87128,22 +87128,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>好樂迪</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>觀光餐旅</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -87156,31 +87156,27 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>新麗</t>
+          <t>好樂迪</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>其他業</t>
+          <t>觀光餐旅</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -87193,27 +87189,31 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>新麗</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>建設營造 / 商用不動產</t>
+          <t>其他業</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -87231,22 +87231,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>三發地產</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>建材營造</t>
+          <t>建設營造 / 商用不動產</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -87259,31 +87259,27 @@
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>三發地產</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>文化創意業</t>
+          <t>建材營造</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -87296,27 +87292,31 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>萬國通</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>塑膠工業</t>
+          <t>文化創意業</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -87329,36 +87329,32 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>萬國通</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>塑膠工業</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>主流</t>
+          <t>非主流</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -87375,27 +87371,27 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>綠能環保</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>非主流</t>
+          <t>主流</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -87403,27 +87399,31 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>世紀鋼</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>綠能環保</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -87436,31 +87436,27 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>provisional_industry_mapping</t>
-        </is>
-      </c>
+      <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>邁達康</t>
+          <t>世紀鋼</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵工業</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -87473,27 +87469,31 @@
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>provisional_industry_mapping</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>有益</t>
+          <t>邁達康</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -87506,7 +87506,40 @@
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr">
+      <c r="K388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>有益</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>非主流</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
         <is>
           <t>provisional_industry_mapping</t>
         </is>
